--- a/AAII_Financials/Quarterly/IMYSY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IMYSY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="92">
   <si>
     <t>IMYSY</t>
   </si>
@@ -656,75 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -761,8 +765,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -799,8 +806,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,8 +847,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -853,8 +866,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -891,8 +905,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -929,8 +946,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -967,8 +987,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1005,8 +1028,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,8 +1044,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1056,8 +1083,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1094,8 +1124,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1110,8 +1143,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1148,8 +1182,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1186,8 +1223,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1224,8 +1264,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1262,8 +1305,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1300,8 +1346,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1338,8 +1387,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1376,8 +1428,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1414,8 +1469,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1452,8 +1510,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1490,8 +1551,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1528,8 +1592,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1566,8 +1633,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1604,8 +1674,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1642,8 +1715,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1680,8 +1756,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1718,51 +1797,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1777,8 +1862,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1793,73 +1879,77 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>585900</v>
+      </c>
+      <c r="E41" s="3">
         <v>552100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>553600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>657400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>649200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>646600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>746900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>662800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>732800</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
         <v>746900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>423700</v>
+      </c>
+      <c r="E42" s="3">
         <v>442100</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>5600</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>744600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -1869,274 +1959,298 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>724100</v>
+      </c>
+      <c r="E43" s="3">
         <v>638300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>698900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>581500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>637000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>702600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>797600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>746300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1120300</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N43" s="3">
         <v>797600</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>850200</v>
+      </c>
+      <c r="E44" s="3">
         <v>819700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>828800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>750300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>741800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>812000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>794900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>844200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1078900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N44" s="3">
         <v>794900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E45" s="3">
         <v>14200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>51800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>40300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>857900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>58900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>499300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1499600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>85100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>499300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2614200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2466200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2133100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2035100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2885900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2964600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2838800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3755000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3017100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N46" s="3">
         <v>2838800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>338400</v>
+      </c>
+      <c r="E47" s="3">
         <v>221400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>184400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>185000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>196100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>140700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>108000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>106700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>118300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N47" s="3">
         <v>108000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2186500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2152800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2177800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2026500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1923300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1915700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1838300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1849600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2177300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N48" s="3">
         <v>1838300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1907600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2014400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2596200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2321300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2359800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2401200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2339500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2286700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2618000</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>2339500</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2173,8 +2287,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2211,46 +2328,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>253500</v>
+      </c>
+      <c r="E52" s="3">
         <v>288700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>290700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>257600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>243200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>356500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>339000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>295500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>328000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N52" s="3">
         <v>339000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2287,46 +2410,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7380300</v>
+      </c>
+      <c r="E54" s="3">
         <v>7230200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7466400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6918900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7700600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7905300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7572900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8411900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8408500</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N54" s="3">
         <v>7572900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2341,8 +2470,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2357,236 +2487,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>551500</v>
+      </c>
+      <c r="E57" s="3">
         <v>409900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>504200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>417200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>444600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>417700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>491200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>577200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>910900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N57" s="3">
         <v>491200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>564900</v>
+      </c>
+      <c r="E58" s="3">
         <v>109900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>100600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>111400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>642500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>626500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>97200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>532800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>433600</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>97200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>426800</v>
+      </c>
+      <c r="E59" s="3">
         <v>261400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>431100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>273400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>574600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>865300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>706200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>838900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>589500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>706200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1543200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1002800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1035900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1018700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1661600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2132500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1294500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2158800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1934000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N60" s="3">
         <v>1294500</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2111500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2513900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2119300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1867100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1929200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2001200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1959500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1915800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1903900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>1959500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>476800</v>
+      </c>
+      <c r="E62" s="3">
         <v>443300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>452100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>419000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>429800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>454600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>441300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>542900</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>454600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2623,8 +2772,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2661,8 +2813,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2699,46 +2854,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4324800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4160000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3814700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3501700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4247900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4415400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3977500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4793800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4769100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N66" s="3">
         <v>3977500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2753,8 +2914,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2791,8 +2953,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2829,8 +2994,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2867,8 +3035,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2905,46 +3076,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-480000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>82800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-98400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>151800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>158600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>253500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>201100</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>158600</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2981,8 +3158,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3019,8 +3199,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3057,46 +3240,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3039900</v>
+      </c>
+      <c r="E76" s="3">
         <v>3053800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3630700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3396600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3414200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3453100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3547800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3567300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3584000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3439700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3547800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3626600</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3133,51 +3322,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3214,8 +3409,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3230,8 +3428,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3268,8 +3467,11 @@
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3306,8 +3508,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3344,8 +3549,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3382,8 +3590,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3420,8 +3631,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3458,8 +3672,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3496,8 +3713,11 @@
       <c r="N89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3512,8 +3732,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3550,8 +3771,11 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3588,8 +3812,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3626,8 +3853,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3664,8 +3894,11 @@
       <c r="N94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3680,8 +3913,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3718,8 +3952,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3756,8 +3993,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3794,8 +4034,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3832,8 +4075,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3870,8 +4116,11 @@
       <c r="N100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3908,8 +4157,11 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3937,13 +4189,16 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>4</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>4</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
